--- a/тест-сьют на переводы.xlsx
+++ b/тест-сьют на переводы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FF9BD1-ACD5-45DD-AF92-E6F23CFFFF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C82449F-B119-4F0F-857C-7D46EB8675F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{EB970A28-A74A-4609-829B-45F6F2401F77}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Тест-кейс №5" sheetId="6" r:id="rId5"/>
     <sheet name="Тест-кейс №6" sheetId="7" r:id="rId6"/>
     <sheet name="Тест-кейс №7" sheetId="8" r:id="rId7"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -610,19 +609,121 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -638,12 +739,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -653,104 +748,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1071,50 +1070,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,198 +1122,209 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="217.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="198" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="229.5" customHeight="1">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="22"/>
+      <c r="D18" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="209.25" customHeight="1">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="38" t="s">
+      <c r="C19" s="22"/>
+      <c r="D19" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="121.5" customHeight="1">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="36"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" ht="57.75" customHeight="1">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="45"/>
-    </row>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
@@ -1322,18 +1332,7 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C13"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{2A6E3475-3196-44EA-B995-60FEF39DD8B3}"/>
@@ -1349,50 +1348,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1401,160 +1400,153 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="227.25" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:4" ht="42" customHeight="1">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="45"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="46"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="46"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1564,6 +1556,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{17EE24EA-BEBA-49BE-ACFA-AB4B2B1B2B41}"/>
@@ -1579,50 +1578,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="56.25" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1631,160 +1630,153 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="163.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:4" ht="45" customHeight="1">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="45"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="46"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="46"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1794,6 +1786,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{13F594F4-CD63-438A-9AFD-BE04E4525D5F}"/>
@@ -1809,50 +1808,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="38">
         <v>4</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1861,172 +1860,165 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="123" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="45"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -2036,6 +2028,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{55166E8C-FD93-442D-8026-1351FEF6E9CF}"/>
@@ -2051,50 +2050,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="38">
         <v>5</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2103,172 +2102,165 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="123" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="45"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -2278,6 +2270,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{B9DB8194-61DB-4728-B702-3DBCC798DC2A}"/>
@@ -2293,50 +2292,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="38">
         <v>5</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2345,172 +2344,165 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="123" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="45"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -2520,6 +2512,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{730436D2-77EF-49D4-A463-A9EC3849F8AA}"/>
@@ -2535,50 +2534,50 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="5" customWidth="1"/>
-    <col min="5" max="7" width="9" style="5"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="34.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="9" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="38">
         <v>5</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2587,172 +2586,165 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="123" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="45"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="5" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="5" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -2762,6 +2754,13 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{64A70F5E-2664-4728-8814-2F0B030CB1B7}"/>
@@ -2770,13 +2769,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F15B62-78D7-4B56-9124-141022CEB2B9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>